--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/148.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/148.xlsx
@@ -426,13 +426,13 @@
         <v>2.678143122444597</v>
       </c>
       <c r="E2">
-        <v>-1.268255564243778</v>
+        <v>-4.119296758466889</v>
       </c>
       <c r="F2">
-        <v>-4.555802316355398</v>
+        <v>-4.206757491857332</v>
       </c>
       <c r="G2">
-        <v>-1.096437280547255</v>
+        <v>-1.454204626430753</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.148635772691125</v>
       </c>
       <c r="E3">
-        <v>-2.241066879045531</v>
+        <v>-5.748542079998515</v>
       </c>
       <c r="F3">
-        <v>-5.017568201237824</v>
+        <v>-4.073499725014511</v>
       </c>
       <c r="G3">
-        <v>-0.6654671516993923</v>
+        <v>-1.281089579091184</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.590838919865829</v>
       </c>
       <c r="E4">
-        <v>-3.617623350949152</v>
+        <v>-5.042639023208852</v>
       </c>
       <c r="F4">
-        <v>-5.158631262684889</v>
+        <v>-4.289580560117069</v>
       </c>
       <c r="G4">
-        <v>0.2458432716234837</v>
+        <v>-0.450182375280587</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.941794490089934</v>
       </c>
       <c r="E5">
-        <v>-2.764938866148869</v>
+        <v>-5.512486315400682</v>
       </c>
       <c r="F5">
-        <v>-5.317759657509371</v>
+        <v>-4.188517158976258</v>
       </c>
       <c r="G5">
-        <v>-0.1300890376339952</v>
+        <v>-0.8201325287486029</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.223593071993706</v>
       </c>
       <c r="E6">
-        <v>-4.340721023545939</v>
+        <v>-7.301192792164405</v>
       </c>
       <c r="F6">
-        <v>-5.312618948107855</v>
+        <v>-4.050699110949929</v>
       </c>
       <c r="G6">
-        <v>-0.2552309695639853</v>
+        <v>-1.662560431035863</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.446893646827911</v>
       </c>
       <c r="E7">
-        <v>-3.526397242064632</v>
+        <v>-6.864312790748414</v>
       </c>
       <c r="F7">
-        <v>-5.338518874648951</v>
+        <v>-4.016130770080674</v>
       </c>
       <c r="G7">
-        <v>-0.2460442056925078</v>
+        <v>-0.6305905544431704</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.630549534252155</v>
       </c>
       <c r="E8">
-        <v>-4.943035237410142</v>
+        <v>-8.142470050939364</v>
       </c>
       <c r="F8">
-        <v>-5.524291537794787</v>
+        <v>-4.394577886751831</v>
       </c>
       <c r="G8">
-        <v>0.2092021535948302</v>
+        <v>-0.0716645299569373</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.798889303895078</v>
       </c>
       <c r="E9">
-        <v>-6.148284066077601</v>
+        <v>-8.413032787475645</v>
       </c>
       <c r="F9">
-        <v>-5.553544169758869</v>
+        <v>-4.547389670532583</v>
       </c>
       <c r="G9">
-        <v>1.094418856977171</v>
+        <v>-1.528261530144249</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.973893240481996</v>
       </c>
       <c r="E10">
-        <v>-6.64449160546808</v>
+        <v>-10.09098184695977</v>
       </c>
       <c r="F10">
-        <v>-5.672059218234865</v>
+        <v>-4.567773549370204</v>
       </c>
       <c r="G10">
-        <v>1.056638911283008</v>
+        <v>0.7824297348107148</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.167252852000275</v>
       </c>
       <c r="E11">
-        <v>-7.493779734762609</v>
+        <v>-11.44085655001019</v>
       </c>
       <c r="F11">
-        <v>-5.12889797597547</v>
+        <v>-4.629339324979956</v>
       </c>
       <c r="G11">
-        <v>1.82701610045357</v>
+        <v>-0.1605592987774472</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.394096908738637</v>
       </c>
       <c r="E12">
-        <v>-8.261125126888343</v>
+        <v>-12.22190963295714</v>
       </c>
       <c r="F12">
-        <v>-5.359742909474713</v>
+        <v>-4.353075289531825</v>
       </c>
       <c r="G12">
-        <v>1.503522832538147</v>
+        <v>0.1850351711581505</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.650537436198905</v>
       </c>
       <c r="E13">
-        <v>-9.295953893225143</v>
+        <v>-12.94248494553166</v>
       </c>
       <c r="F13">
-        <v>-4.822035158535135</v>
+        <v>-4.333589371948258</v>
       </c>
       <c r="G13">
-        <v>2.440562815792239</v>
+        <v>0.2503588557390496</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.934993363279168</v>
       </c>
       <c r="E14">
-        <v>-10.66099445572726</v>
+        <v>-13.29871735334505</v>
       </c>
       <c r="F14">
-        <v>-5.014308142610892</v>
+        <v>-3.836604243065332</v>
       </c>
       <c r="G14">
-        <v>1.957620432523358</v>
+        <v>1.168383065415568</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.228374673745983</v>
       </c>
       <c r="E15">
-        <v>-11.0392216617959</v>
+        <v>-14.15253395664725</v>
       </c>
       <c r="F15">
-        <v>-4.713989198013151</v>
+        <v>-3.402420972259157</v>
       </c>
       <c r="G15">
-        <v>3.20426925570117</v>
+        <v>1.554005341466493</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>6.500808774798826</v>
       </c>
       <c r="E16">
-        <v>-12.85071089129221</v>
+        <v>-15.31596232785387</v>
       </c>
       <c r="F16">
-        <v>-4.165922426680684</v>
+        <v>-2.816251820307131</v>
       </c>
       <c r="G16">
-        <v>3.029906132693295</v>
+        <v>2.061157744264064</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>6.719917123235732</v>
       </c>
       <c r="E17">
-        <v>-13.37865850500245</v>
+        <v>-15.4028818579571</v>
       </c>
       <c r="F17">
-        <v>-4.052641526255216</v>
+        <v>-3.063347952057656</v>
       </c>
       <c r="G17">
-        <v>3.341597305761217</v>
+        <v>1.863117599559323</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.844103499397084</v>
       </c>
       <c r="E18">
-        <v>-15.3676412732294</v>
+        <v>-17.37208878019255</v>
       </c>
       <c r="F18">
-        <v>-3.524022663564344</v>
+        <v>-2.9809691133072</v>
       </c>
       <c r="G18">
-        <v>4.071076015339623</v>
+        <v>3.056198485366187</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.841416675265896</v>
       </c>
       <c r="E19">
-        <v>-14.88388703736002</v>
+        <v>-17.52708486005308</v>
       </c>
       <c r="F19">
-        <v>-3.894833150311252</v>
+        <v>-2.783861075071606</v>
       </c>
       <c r="G19">
-        <v>3.913394731304136</v>
+        <v>2.210721570637258</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.67901895318039</v>
       </c>
       <c r="E20">
-        <v>-17.53629124771068</v>
+        <v>-19.86975503370111</v>
       </c>
       <c r="F20">
-        <v>-2.865779847253627</v>
+        <v>-1.920014430141921</v>
       </c>
       <c r="G20">
-        <v>4.237397823232607</v>
+        <v>2.670205428214863</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.338887940467992</v>
       </c>
       <c r="E21">
-        <v>-18.18126821520114</v>
+        <v>-20.32033819746431</v>
       </c>
       <c r="F21">
-        <v>-2.387277358256837</v>
+        <v>-2.00421532254809</v>
       </c>
       <c r="G21">
-        <v>3.943570353894593</v>
+        <v>2.757696525726722</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.811850568344663</v>
       </c>
       <c r="E22">
-        <v>-17.34613609565459</v>
+        <v>-20.38475121174942</v>
       </c>
       <c r="F22">
-        <v>-2.001633090052966</v>
+        <v>-1.572984079568294</v>
       </c>
       <c r="G22">
-        <v>4.519780736641361</v>
+        <v>2.52622649216642</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.09958792673998</v>
       </c>
       <c r="E23">
-        <v>-18.14689709748292</v>
+        <v>-22.04101340921081</v>
       </c>
       <c r="F23">
-        <v>-2.320007865792631</v>
+        <v>-0.9362139399120628</v>
       </c>
       <c r="G23">
-        <v>3.336939368187462</v>
+        <v>2.914765358837443</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.220948284255263</v>
       </c>
       <c r="E24">
-        <v>-18.75711349849052</v>
+        <v>-20.76145232207747</v>
       </c>
       <c r="F24">
-        <v>-1.783438799406253</v>
+        <v>-1.18080860816915</v>
       </c>
       <c r="G24">
-        <v>3.927898231311683</v>
+        <v>3.862653999823727</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.19530350220362</v>
       </c>
       <c r="E25">
-        <v>-18.88531912612167</v>
+        <v>-21.64913285400904</v>
       </c>
       <c r="F25">
-        <v>-1.2251159485654</v>
+        <v>-0.9586368401158122</v>
       </c>
       <c r="G25">
-        <v>3.710368905017252</v>
+        <v>2.08161691569676</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.059296034862255</v>
       </c>
       <c r="E26">
-        <v>-18.34173922013695</v>
+        <v>-22.01699891154813</v>
       </c>
       <c r="F26">
-        <v>-1.697354088813669</v>
+        <v>-0.8974582806023863</v>
       </c>
       <c r="G26">
-        <v>2.868414410742107</v>
+        <v>1.847561346070287</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.847763173368314</v>
       </c>
       <c r="E27">
-        <v>-19.25381464154783</v>
+        <v>-21.08930025481079</v>
       </c>
       <c r="F27">
-        <v>-1.192890700598038</v>
+        <v>-0.4152617975578337</v>
       </c>
       <c r="G27">
-        <v>2.548873934200574</v>
+        <v>2.672552605002206</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.4002586836240521</v>
       </c>
       <c r="E28">
-        <v>-19.50543024283602</v>
+        <v>-21.77951667763788</v>
       </c>
       <c r="F28">
-        <v>-1.28075074552183</v>
+        <v>-0.2396105989175714</v>
       </c>
       <c r="G28">
-        <v>2.063534715961261</v>
+        <v>2.050342191987265</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.6364564299805</v>
       </c>
       <c r="E29">
-        <v>-19.31432863971233</v>
+        <v>-21.39996262868499</v>
       </c>
       <c r="F29">
-        <v>-1.258941531360313</v>
+        <v>-0.4684355155216709</v>
       </c>
       <c r="G29">
-        <v>1.614121537914119</v>
+        <v>2.652166265571374</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.822326449590488</v>
       </c>
       <c r="E30">
-        <v>-18.35597674241707</v>
+        <v>-21.67783885074366</v>
       </c>
       <c r="F30">
-        <v>-1.006323017082652</v>
+        <v>-0.6165444845865258</v>
       </c>
       <c r="G30">
-        <v>1.011555902129213</v>
+        <v>1.10831983769657</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.91127467722919</v>
       </c>
       <c r="E31">
-        <v>-18.65711573545314</v>
+        <v>-20.6776302681955</v>
       </c>
       <c r="F31">
-        <v>-1.008035003177242</v>
+        <v>-0.6566660902482687</v>
       </c>
       <c r="G31">
-        <v>1.534142068230866</v>
+        <v>1.045293671719925</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.865709284075165</v>
       </c>
       <c r="E32">
-        <v>-18.07716765471282</v>
+        <v>-19.60896021559938</v>
       </c>
       <c r="F32">
-        <v>-1.241516807025691</v>
+        <v>-0.7164011018197715</v>
       </c>
       <c r="G32">
-        <v>0.8854373592651378</v>
+        <v>0.7048934477354443</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.655951332653172</v>
       </c>
       <c r="E33">
-        <v>-16.83254374454867</v>
+        <v>-20.62016393303816</v>
       </c>
       <c r="F33">
-        <v>-1.460914714168137</v>
+        <v>-1.266382573604006</v>
       </c>
       <c r="G33">
-        <v>0.5573689174144417</v>
+        <v>1.540577768759209</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.25298670332699</v>
       </c>
       <c r="E34">
-        <v>-16.47473542778061</v>
+        <v>-18.92457193882016</v>
       </c>
       <c r="F34">
-        <v>-1.424749205883162</v>
+        <v>-1.038676545229164</v>
       </c>
       <c r="G34">
-        <v>1.184644465104468</v>
+        <v>0.3377407052481126</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.643194115900879</v>
       </c>
       <c r="E35">
-        <v>-16.10379453639031</v>
+        <v>-19.42900318700856</v>
       </c>
       <c r="F35">
-        <v>-1.619448427421372</v>
+        <v>-1.09903553693135</v>
       </c>
       <c r="G35">
-        <v>1.195691755569016</v>
+        <v>0.7129645577601875</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.818596662562368</v>
       </c>
       <c r="E36">
-        <v>-15.68111130098836</v>
+        <v>-17.85793969952749</v>
       </c>
       <c r="F36">
-        <v>-1.242922346025643</v>
+        <v>-1.426816733955768</v>
       </c>
       <c r="G36">
-        <v>1.628783944107551</v>
+        <v>0.6878077222072657</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.783718460482189</v>
       </c>
       <c r="E37">
-        <v>-14.17103277296858</v>
+        <v>-18.05672159456818</v>
       </c>
       <c r="F37">
-        <v>-1.810672998181108</v>
+        <v>-1.229959713107772</v>
       </c>
       <c r="G37">
-        <v>1.357054366244172</v>
+        <v>0.9225187798505143</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.553429964242011</v>
       </c>
       <c r="E38">
-        <v>-14.08507327935498</v>
+        <v>-17.76756494375641</v>
       </c>
       <c r="F38">
-        <v>-1.543340272243098</v>
+        <v>-1.065231334166295</v>
       </c>
       <c r="G38">
-        <v>1.384276982213599</v>
+        <v>0.4828783322353007</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.150644437467351</v>
       </c>
       <c r="E39">
-        <v>-13.82591776884402</v>
+        <v>-15.91226272823589</v>
       </c>
       <c r="F39">
-        <v>-1.518381858868731</v>
+        <v>-0.9211418107148255</v>
       </c>
       <c r="G39">
-        <v>1.201428930988573</v>
+        <v>2.212747624507292</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.605572757506839</v>
       </c>
       <c r="E40">
-        <v>-13.48582484239397</v>
+        <v>-16.3024586911068</v>
       </c>
       <c r="F40">
-        <v>-2.115235482779268</v>
+        <v>-0.4937629323743363</v>
       </c>
       <c r="G40">
-        <v>2.048667055944394</v>
+        <v>1.308376104634728</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.953440204936618</v>
       </c>
       <c r="E41">
-        <v>-13.33483646203023</v>
+        <v>-14.87911402575593</v>
       </c>
       <c r="F41">
-        <v>-2.075547812538356</v>
+        <v>-1.550360840566241</v>
       </c>
       <c r="G41">
-        <v>2.631693851956521</v>
+        <v>1.488284391420882</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.235132498682106</v>
       </c>
       <c r="E42">
-        <v>-11.74130268652309</v>
+        <v>-14.10734431452471</v>
       </c>
       <c r="F42">
-        <v>-2.065698745450238</v>
+        <v>-1.225177713096102</v>
       </c>
       <c r="G42">
-        <v>1.904972826812328</v>
+        <v>2.086811161647877</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.486971433051843</v>
       </c>
       <c r="E43">
-        <v>-12.43144665376606</v>
+        <v>-13.33814224805583</v>
       </c>
       <c r="F43">
-        <v>-1.909914345666206</v>
+        <v>-1.780360866959597</v>
       </c>
       <c r="G43">
-        <v>2.427923152923301</v>
+        <v>3.203484656408362</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.748464513937567</v>
       </c>
       <c r="E44">
-        <v>-11.41899760597517</v>
+        <v>-12.50133006465243</v>
       </c>
       <c r="F44">
-        <v>-1.842337614254404</v>
+        <v>-1.613776384685226</v>
       </c>
       <c r="G44">
-        <v>2.874744173813194</v>
+        <v>2.923290013601067</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.049386745538443</v>
       </c>
       <c r="E45">
-        <v>-9.690506248091438</v>
+        <v>-12.30713098530749</v>
       </c>
       <c r="F45">
-        <v>-2.18364207609076</v>
+        <v>-1.7023372194766</v>
       </c>
       <c r="G45">
-        <v>2.990984048788084</v>
+        <v>2.049825746883139</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.412261155242291</v>
       </c>
       <c r="E46">
-        <v>-8.198066126331534</v>
+        <v>-12.59474795495666</v>
       </c>
       <c r="F46">
-        <v>-2.00426045816668</v>
+        <v>-1.695859862282452</v>
       </c>
       <c r="G46">
-        <v>2.71037558778838</v>
+        <v>2.41053285720551</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.8567117075361697</v>
       </c>
       <c r="E47">
-        <v>-9.488155915532696</v>
+        <v>-11.54492541118046</v>
       </c>
       <c r="F47">
-        <v>-2.350052350714433</v>
+        <v>-2.017308611203986</v>
       </c>
       <c r="G47">
-        <v>3.460114836067125</v>
+        <v>2.204004473738077</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.3864651434985694</v>
       </c>
       <c r="E48">
-        <v>-8.567263555228882</v>
+        <v>-11.10366184692505</v>
       </c>
       <c r="F48">
-        <v>-2.620048870002211</v>
+        <v>-1.619429422950387</v>
       </c>
       <c r="G48">
-        <v>3.552641273344216</v>
+        <v>2.861975399668225</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.006957711207920655</v>
       </c>
       <c r="E49">
-        <v>-8.36643026146271</v>
+        <v>-9.748968847530463</v>
       </c>
       <c r="F49">
-        <v>-2.471700761344125</v>
+        <v>-1.719878346196007</v>
       </c>
       <c r="G49">
-        <v>3.616653981891564</v>
+        <v>1.651918036335978</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.2865408138323021</v>
       </c>
       <c r="E50">
-        <v>-8.484569091374814</v>
+        <v>-9.935206869569914</v>
       </c>
       <c r="F50">
-        <v>-2.394863309591792</v>
+        <v>-1.621551588877076</v>
       </c>
       <c r="G50">
-        <v>3.426112222833271</v>
+        <v>2.297762433955776</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.5039719525836174</v>
       </c>
       <c r="E51">
-        <v>-6.70583884284999</v>
+        <v>-9.905699332935933</v>
       </c>
       <c r="F51">
-        <v>-2.346137429691467</v>
+        <v>-1.64859495108912</v>
       </c>
       <c r="G51">
-        <v>3.736333513681756</v>
+        <v>1.485708786991329</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.6550715274216332</v>
       </c>
       <c r="E52">
-        <v>-7.298756473148278</v>
+        <v>-8.878043669427283</v>
       </c>
       <c r="F52">
-        <v>-2.285954229345894</v>
+        <v>-1.682864763393314</v>
       </c>
       <c r="G52">
-        <v>3.019967874984403</v>
+        <v>2.167820210993843</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.7583602778345734</v>
       </c>
       <c r="E53">
-        <v>-5.553686371922467</v>
+        <v>-7.741106871165534</v>
       </c>
       <c r="F53">
-        <v>-2.698785185147157</v>
+        <v>-1.728898343237392</v>
       </c>
       <c r="G53">
-        <v>3.576235531402602</v>
+        <v>2.072201724183073</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.8282941213024784</v>
       </c>
       <c r="E54">
-        <v>-3.877874752169967</v>
+        <v>-6.37256579825549</v>
       </c>
       <c r="F54">
-        <v>-2.519371893104768</v>
+        <v>-1.37331677257335</v>
       </c>
       <c r="G54">
-        <v>3.207520211420734</v>
+        <v>2.008404201095778</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.8825850953534765</v>
       </c>
       <c r="E55">
-        <v>-5.762263356241756</v>
+        <v>-7.343950643744828</v>
       </c>
       <c r="F55">
-        <v>-2.465129965500967</v>
+        <v>-1.691088156359233</v>
       </c>
       <c r="G55">
-        <v>3.957338912792422</v>
+        <v>1.052907926460249</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.9358496610882264</v>
       </c>
       <c r="E56">
-        <v>-3.365310364663782</v>
+        <v>-6.630389937408194</v>
       </c>
       <c r="F56">
-        <v>-2.264924990347732</v>
+        <v>-1.865977592454169</v>
       </c>
       <c r="G56">
-        <v>2.787253076301335</v>
+        <v>1.763738333015941</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.9999674319031087</v>
       </c>
       <c r="E57">
-        <v>-4.288113740998832</v>
+        <v>-5.684808336814562</v>
       </c>
       <c r="F57">
-        <v>-3.015228631522944</v>
+        <v>-1.729230129626677</v>
       </c>
       <c r="G57">
-        <v>1.96896567208644</v>
+        <v>0.8051036612091832</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.085299405990117</v>
       </c>
       <c r="E58">
-        <v>-4.350878390745144</v>
+        <v>-4.771895147712264</v>
       </c>
       <c r="F58">
-        <v>-2.574693908142899</v>
+        <v>-1.421101139306947</v>
       </c>
       <c r="G58">
-        <v>2.059283975488837</v>
+        <v>1.159884895016258</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.196203597771416</v>
       </c>
       <c r="E59">
-        <v>-2.766202310397009</v>
+        <v>-3.426376836657217</v>
       </c>
       <c r="F59">
-        <v>-2.885643478698027</v>
+        <v>-1.882444966562908</v>
       </c>
       <c r="G59">
-        <v>2.228638243095793</v>
+        <v>0.1664828739560748</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.336929835538743</v>
       </c>
       <c r="E60">
-        <v>-3.382581964529037</v>
+        <v>-6.499566851800605</v>
       </c>
       <c r="F60">
-        <v>-2.433567498459217</v>
+        <v>-2.365396085476168</v>
       </c>
       <c r="G60">
-        <v>1.840940254991745</v>
+        <v>0.4005682384924012</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.503967930456909</v>
       </c>
       <c r="E61">
-        <v>-2.207293519896326</v>
+        <v>-4.772741972351699</v>
       </c>
       <c r="F61">
-        <v>-3.051824115963961</v>
+        <v>-2.32836666561432</v>
       </c>
       <c r="G61">
-        <v>2.448981533098605</v>
+        <v>0.974385096814276</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.694614697354067</v>
       </c>
       <c r="E62">
-        <v>-2.189818138700726</v>
+        <v>-2.96404681131812</v>
       </c>
       <c r="F62">
-        <v>-2.772041085971724</v>
+        <v>-2.49521245936474</v>
       </c>
       <c r="G62">
-        <v>1.735956234850377</v>
+        <v>-0.5417951019888386</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.902864298092728</v>
       </c>
       <c r="E63">
-        <v>-3.283204602430711</v>
+        <v>-4.408530393336795</v>
       </c>
       <c r="F63">
-        <v>-2.721483650180193</v>
+        <v>-1.910611968121957</v>
       </c>
       <c r="G63">
-        <v>1.845839862389866</v>
+        <v>0.2325679840110063</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>2.119726695290006</v>
       </c>
       <c r="E64">
-        <v>-1.702115073496651</v>
+        <v>-3.833753829913234</v>
       </c>
       <c r="F64">
-        <v>-2.967277975668226</v>
+        <v>-2.573764272770536</v>
       </c>
       <c r="G64">
-        <v>0.8740755669743591</v>
+        <v>-0.03619865559472507</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>2.339661022324731</v>
       </c>
       <c r="E65">
-        <v>-1.920713570794915</v>
+        <v>-3.601619723806044</v>
       </c>
       <c r="F65">
-        <v>-2.938678622394263</v>
+        <v>-2.000708205798349</v>
       </c>
       <c r="G65">
-        <v>1.722379687593826</v>
+        <v>-0.7047070479763737</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>2.551793722084243</v>
       </c>
       <c r="E66">
-        <v>-1.240740556173173</v>
+        <v>-3.14861382644874</v>
       </c>
       <c r="F66">
-        <v>-3.093264156800307</v>
+        <v>-2.565451400420394</v>
       </c>
       <c r="G66">
-        <v>1.000127898927649</v>
+        <v>-0.6812121062841661</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>2.749703885368673</v>
       </c>
       <c r="E67">
-        <v>-0.8479497776958611</v>
+        <v>-2.874613978140637</v>
       </c>
       <c r="F67">
-        <v>-3.096154420095984</v>
+        <v>-2.200733430330182</v>
       </c>
       <c r="G67">
-        <v>0.9043174004756014</v>
+        <v>-0.9440992170121517</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>2.926420508444035</v>
       </c>
       <c r="E68">
-        <v>-1.105416167401959</v>
+        <v>-2.864347927565249</v>
       </c>
       <c r="F68">
-        <v>-3.161830704409258</v>
+        <v>-2.998136485430563</v>
       </c>
       <c r="G68">
-        <v>1.080762856627677</v>
+        <v>-0.7719309856968144</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>3.074605290290825</v>
       </c>
       <c r="E69">
-        <v>-1.341508159791853</v>
+        <v>-2.505706371579779</v>
       </c>
       <c r="F69">
-        <v>-3.205843475505235</v>
+        <v>-2.965275379538153</v>
       </c>
       <c r="G69">
-        <v>0.7499665252526215</v>
+        <v>-0.4666556498840004</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>3.193886415472049</v>
       </c>
       <c r="E70">
-        <v>-0.9550572449252803</v>
+        <v>-2.560442036910491</v>
       </c>
       <c r="F70">
-        <v>-3.458335293309662</v>
+        <v>-2.643484550138885</v>
       </c>
       <c r="G70">
-        <v>0.9068863838140758</v>
+        <v>-1.296765012219633</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>3.281123917783493</v>
       </c>
       <c r="E71">
-        <v>-0.3163567424094454</v>
+        <v>-1.734135913204889</v>
       </c>
       <c r="F71">
-        <v>-3.353268283614621</v>
+        <v>-2.201564875935788</v>
       </c>
       <c r="G71">
-        <v>1.250948071164991</v>
+        <v>-1.740752206127909</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>3.339498540143456</v>
       </c>
       <c r="E72">
-        <v>-2.256463690671611</v>
+        <v>-3.550674391219753</v>
       </c>
       <c r="F72">
-        <v>-3.255220258536807</v>
+        <v>-2.186537090504183</v>
       </c>
       <c r="G72">
-        <v>0.6701889988472645</v>
+        <v>-1.213753082822408</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>3.372833788371628</v>
       </c>
       <c r="E73">
-        <v>-1.644549111911146</v>
+        <v>-2.708840130141849</v>
       </c>
       <c r="F73">
-        <v>-3.46917417659493</v>
+        <v>-3.048355800009148</v>
       </c>
       <c r="G73">
-        <v>1.132705316138842</v>
+        <v>0.2705531835286039</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>3.384317936329314</v>
       </c>
       <c r="E74">
-        <v>-2.534108960555888</v>
+        <v>-3.264710314583385</v>
       </c>
       <c r="F74">
-        <v>-3.255129987299627</v>
+        <v>-2.970150026345875</v>
       </c>
       <c r="G74">
-        <v>1.36051388633271</v>
+        <v>0.6954914984039141</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>3.382061911299636</v>
       </c>
       <c r="E75">
-        <v>-2.316302946208967</v>
+        <v>-2.866643863887138</v>
       </c>
       <c r="F75">
-        <v>-3.268475085196077</v>
+        <v>-3.096724554225542</v>
       </c>
       <c r="G75">
-        <v>1.707124693748864</v>
+        <v>-0.3731095645808145</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>3.368282161071212</v>
       </c>
       <c r="E76">
-        <v>-2.449326870184283</v>
+        <v>-3.365486975150081</v>
       </c>
       <c r="F76">
-        <v>-3.850293796998391</v>
+        <v>-3.234013644476115</v>
       </c>
       <c r="G76">
-        <v>1.571680344100662</v>
+        <v>-0.1879375103872199</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.348640459680024</v>
       </c>
       <c r="E77">
-        <v>-2.780820224493769</v>
+        <v>-5.471458340891188</v>
       </c>
       <c r="F77">
-        <v>-3.898158932733675</v>
+        <v>-3.571946396418499</v>
       </c>
       <c r="G77">
-        <v>1.333427002730393</v>
+        <v>-0.09492442291585666</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.324117489340253</v>
       </c>
       <c r="E78">
-        <v>-3.123118517785556</v>
+        <v>-5.963422700136481</v>
       </c>
       <c r="F78">
-        <v>-3.734640505111594</v>
+        <v>-3.235328912238887</v>
       </c>
       <c r="G78">
-        <v>1.96401640650523</v>
+        <v>0.01975618511003653</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>3.292026925158259</v>
       </c>
       <c r="E79">
-        <v>-3.795628607242658</v>
+        <v>-6.593673070154003</v>
       </c>
       <c r="F79">
-        <v>-4.018763681165092</v>
+        <v>-3.12256509179481</v>
       </c>
       <c r="G79">
-        <v>1.264782840973605</v>
+        <v>-0.1680874793337499</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.24994024227035</v>
       </c>
       <c r="E80">
-        <v>-4.286641986946339</v>
+        <v>-6.593885908432363</v>
       </c>
       <c r="F80">
-        <v>-3.67347857451028</v>
+        <v>-3.408642560947961</v>
       </c>
       <c r="G80">
-        <v>2.337896177528361</v>
+        <v>0.6377125471070141</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.187937001126056</v>
       </c>
       <c r="E81">
-        <v>-5.3960728340855</v>
+        <v>-6.657003779151273</v>
       </c>
       <c r="F81">
-        <v>-4.291728857191362</v>
+        <v>-3.395837506768675</v>
       </c>
       <c r="G81">
-        <v>3.025575939127929</v>
+        <v>1.158477913162068</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.098899252342605</v>
       </c>
       <c r="E82">
-        <v>-6.442539778622012</v>
+        <v>-8.071893783529822</v>
       </c>
       <c r="F82">
-        <v>-4.124730235820103</v>
+        <v>-3.494340847297178</v>
       </c>
       <c r="G82">
-        <v>2.635398352414966</v>
+        <v>1.124915602484937</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.97073406509494</v>
       </c>
       <c r="E83">
-        <v>-6.648730257139259</v>
+        <v>-8.304603005835986</v>
       </c>
       <c r="F83">
-        <v>-4.347977340190026</v>
+        <v>-4.039569617629178</v>
       </c>
       <c r="G83">
-        <v>2.382846764860585</v>
+        <v>1.451673068302082</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.793620938214583</v>
       </c>
       <c r="E84">
-        <v>-8.644791030240199</v>
+        <v>-9.495111651608477</v>
       </c>
       <c r="F84">
-        <v>-4.287113938153772</v>
+        <v>-3.994903567843082</v>
       </c>
       <c r="G84">
-        <v>2.293796400399729</v>
+        <v>1.61084740837578</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.558806214670723</v>
       </c>
       <c r="E85">
-        <v>-9.922029010207593</v>
+        <v>-10.64176202661668</v>
       </c>
       <c r="F85">
-        <v>-4.509384687826826</v>
+        <v>-3.735092653150452</v>
       </c>
       <c r="G85">
-        <v>2.596145213955827</v>
+        <v>0.9752259753812509</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.257765103361062</v>
       </c>
       <c r="E86">
-        <v>-11.55431293779837</v>
+        <v>-12.27443540297211</v>
       </c>
       <c r="F86">
-        <v>-4.466512184989964</v>
+        <v>-3.391218628466296</v>
       </c>
       <c r="G86">
-        <v>2.716377606851078</v>
+        <v>2.125590892094899</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.88954443943811</v>
       </c>
       <c r="E87">
-        <v>-12.36913032294651</v>
+        <v>-12.8582009873009</v>
       </c>
       <c r="F87">
-        <v>-4.90836613539757</v>
+        <v>-3.86290643090895</v>
       </c>
       <c r="G87">
-        <v>3.252407898387712</v>
+        <v>2.072555952555775</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.450807745221961</v>
       </c>
       <c r="E88">
-        <v>-13.6121239824679</v>
+        <v>-15.25122326344021</v>
       </c>
       <c r="F88">
-        <v>-4.52292616525679</v>
+        <v>-3.974518105299545</v>
       </c>
       <c r="G88">
-        <v>2.953882764929472</v>
+        <v>2.233455086855433</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.9482906045307534</v>
       </c>
       <c r="E89">
-        <v>-15.89229215786206</v>
+        <v>-16.45112396430461</v>
       </c>
       <c r="F89">
-        <v>-4.702509705685089</v>
+        <v>-4.205046297615699</v>
       </c>
       <c r="G89">
-        <v>2.526418503807697</v>
+        <v>1.991599871938437</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.388007633265208</v>
       </c>
       <c r="E90">
-        <v>-17.10554732857508</v>
+        <v>-18.35035690617355</v>
       </c>
       <c r="F90">
-        <v>-4.990654702910846</v>
+        <v>-3.80795579490799</v>
       </c>
       <c r="G90">
-        <v>2.2076229000125</v>
+        <v>1.565764399221985</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.2198806788016891</v>
       </c>
       <c r="E91">
-        <v>-18.40400573774242</v>
+        <v>-20.08544172221244</v>
       </c>
       <c r="F91">
-        <v>-4.512118956089831</v>
+        <v>-3.775919007944565</v>
       </c>
       <c r="G91">
-        <v>2.661131222891721</v>
+        <v>0.8763068746678279</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.858503345909404</v>
       </c>
       <c r="E92">
-        <v>-20.39411156752327</v>
+        <v>-21.62562554543522</v>
       </c>
       <c r="F92">
-        <v>-4.62068041288729</v>
+        <v>-3.750142610464873</v>
       </c>
       <c r="G92">
-        <v>2.306697596366269</v>
+        <v>0.8230004703944832</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.517980602266349</v>
       </c>
       <c r="E93">
-        <v>-22.91695160804047</v>
+        <v>-24.07606887199179</v>
       </c>
       <c r="F93">
-        <v>-4.821418305081071</v>
+        <v>-3.923312141935642</v>
       </c>
       <c r="G93">
-        <v>1.050007888567848</v>
+        <v>1.075992360505587</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.179823420664368</v>
       </c>
       <c r="E94">
-        <v>-25.40273514575291</v>
+        <v>-26.25581813626587</v>
       </c>
       <c r="F94">
-        <v>-4.960645059519184</v>
+        <v>-3.970252393416309</v>
       </c>
       <c r="G94">
-        <v>1.798499061178288</v>
+        <v>0.4788030506764578</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.834272019807633</v>
       </c>
       <c r="E95">
-        <v>-26.44292562531479</v>
+        <v>-28.2737786096679</v>
       </c>
       <c r="F95">
-        <v>-4.803609532061954</v>
+        <v>-4.090321057395351</v>
       </c>
       <c r="G95">
-        <v>0.9570643225528092</v>
+        <v>0.9189599433957978</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.472248108476377</v>
       </c>
       <c r="E96">
-        <v>-30.01865172227438</v>
+        <v>-31.11535076474097</v>
       </c>
       <c r="F96">
-        <v>-4.408765516195295</v>
+        <v>-4.038500616136257</v>
       </c>
       <c r="G96">
-        <v>0.8713940250875494</v>
+        <v>0.5287360090452852</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.07854586018342</v>
       </c>
       <c r="E97">
-        <v>-32.05488685253437</v>
+        <v>-32.32607678272071</v>
       </c>
       <c r="F97">
-        <v>-5.169183495199461</v>
+        <v>-3.463213107529215</v>
       </c>
       <c r="G97">
-        <v>0.4230203583397384</v>
+        <v>0.07765431604635033</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.652500118512024</v>
       </c>
       <c r="E98">
-        <v>-33.54295020416586</v>
+        <v>-34.54471205329865</v>
       </c>
       <c r="F98">
-        <v>-4.555923469857929</v>
+        <v>-4.314667253670588</v>
       </c>
       <c r="G98">
-        <v>-0.3960516451679638</v>
+        <v>-0.1740961194875271</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.17519965571621</v>
       </c>
       <c r="E99">
-        <v>-37.62819755409847</v>
+        <v>-37.79719341135372</v>
       </c>
       <c r="F99">
-        <v>-4.859724191910763</v>
+        <v>-3.895803170184458</v>
       </c>
       <c r="G99">
-        <v>0.1647249742747218</v>
+        <v>-0.7398153834203446</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.650719920483078</v>
       </c>
       <c r="E100">
-        <v>-39.87462859813549</v>
+        <v>-39.61594178468432</v>
       </c>
       <c r="F100">
-        <v>-5.00117209389528</v>
+        <v>-4.437226295201658</v>
       </c>
       <c r="G100">
-        <v>-1.19666404674869</v>
+        <v>-0.4106974986336996</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.056428273923269</v>
       </c>
       <c r="E101">
-        <v>-41.37738005521086</v>
+        <v>-43.35669226719443</v>
       </c>
       <c r="F101">
-        <v>-4.917927759862035</v>
+        <v>-4.082716893442369</v>
       </c>
       <c r="G101">
-        <v>-1.060752910179451</v>
+        <v>-1.766978347890016</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.40377011140337</v>
       </c>
       <c r="E102">
-        <v>-44.66588089552295</v>
+        <v>-46.70859627208791</v>
       </c>
       <c r="F102">
-        <v>-4.971914710813451</v>
+        <v>-4.021227135716559</v>
       </c>
       <c r="G102">
-        <v>-1.672465583289363</v>
+        <v>-1.983219871969671</v>
       </c>
     </row>
   </sheetData>
